--- a/Apostas_Diarias/apostas_reais_consolidado.xlsx
+++ b/Apostas_Diarias/apostas_reais_consolidado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J126"/>
+  <dimension ref="A1:J92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,22 +471,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1 ⭐</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BRAZIL 1</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Chapecoense x Atletico MG</t>
+          <t>Andorra CF x Malaga</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="G2" t="n">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="H2" t="n">
         <v>500</v>
@@ -509,40 +509,40 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>61.51315789473684</v>
+        <v>38.95833333333334</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BRAZIL 1</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino x Flamengo</t>
+          <t>Andorra CF x Malaga</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lay_CS_0x1_B365</t>
+          <t>Lay_CS_1x0_B365</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="H3" t="n">
         <v>500</v>
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>61.51315789473684</v>
+        <v>46.75</v>
       </c>
     </row>
     <row r="4">
@@ -569,12 +569,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ROMANIA 1</t>
+          <t>NETHERLANDS 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Botosani x FCSB</t>
+          <t>MVV Maastricht x RKC Waalwijk</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="G4" t="n">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="H4" t="n">
         <v>500</v>
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>53.125</v>
+        <v>38.95833333333334</v>
       </c>
     </row>
     <row r="5">
@@ -608,17 +608,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FRANCE 2</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Annecy x Guingamp</t>
+          <t>Cadiz x Cordoba</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -627,10 +627,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="G5" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="H5" t="n">
         <v>500</v>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>49.21052631578947</v>
+        <v>44.52380952380953</v>
       </c>
     </row>
     <row r="6">
@@ -652,17 +652,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FRANCE 2</t>
+          <t>SLOVAKIA 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Grenoble x Clermont</t>
+          <t>Tatran Presov x Ruzomberok</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -671,10 +671,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="G6" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="H6" t="n">
         <v>500</v>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>49.21052631578947</v>
+        <v>37.40000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -701,12 +701,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ROMANIA 1</t>
+          <t>SLOVAKIA 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Otelul Galati x Hermannstadt</t>
+          <t>Zemplin x Zilina</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="G7" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="H7" t="n">
         <v>500</v>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>49.21052631578947</v>
+        <v>44.52380952380953</v>
       </c>
     </row>
     <row r="8">
@@ -745,12 +745,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SLOVAKIA 1</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Zemplin x Zilina</t>
+          <t>Albacete x Burgos</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -759,10 +759,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="G8" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="H8" t="n">
         <v>500</v>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>44.52380952380953</v>
+        <v>54.36046511627907</v>
       </c>
     </row>
     <row r="9">
@@ -789,12 +789,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SCOTLAND 2</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ayr x Partick</t>
+          <t>Leonesa x Valladolid</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H9" t="n">
         <v>500</v>
@@ -817,40 +817,40 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>44.52380952380953</v>
+        <v>53.125</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P1 ⭐</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CHINA 1</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Tianjin Jinmen Tiger FC x Shanghai Shenhua</t>
+          <t>Albacete x Burgos</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lay_CS_0x1_B365</t>
+          <t>Lay_CS_1x0_B365</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="G10" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="H10" t="n">
         <v>500</v>
@@ -861,40 +861,40 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>49.21052631578947</v>
+        <v>70.83333333333334</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P1 ⭐</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SWEDEN 1</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Kalmar FF x Vasteras SK</t>
+          <t>Leonesa x Valladolid</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lay_CS_0x1_B365</t>
+          <t>Lay_CS_1x0_B365</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="H11" t="n">
         <v>500</v>
@@ -921,12 +921,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SWEDEN 2</t>
+          <t>ITALY 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sundsvall x United IK Nordic</t>
+          <t>US Cremonese x Bologna</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -935,10 +935,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="G12" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="H12" t="n">
         <v>500</v>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>44.52380952380953</v>
+        <v>54.36046511627907</v>
       </c>
     </row>
     <row r="13">
@@ -965,12 +965,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ITALY 1</t>
+          <t>GERMANY 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>US Cremonese x Bologna</t>
+          <t>Union Berlin x St Pauli</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="G13" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="H13" t="n">
         <v>500</v>
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>54.36046511627907</v>
+        <v>40.65217391304348</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P1 ⭐</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SERBIA 1</t>
+          <t>ITALY 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Radnik Surdulica x Crvena Zvezda</t>
+          <t>Pisa x Torino</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1023,21 +1023,21 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="G14" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="H14" t="n">
         <v>500</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>46.75</v>
+        <v>-500</v>
       </c>
     </row>
     <row r="15">
@@ -1048,17 +1048,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SCOTLAND 1</t>
+          <t>NETHERLANDS 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Dundee x Celtic</t>
+          <t>Helmond Sport x RKC Waalwijk</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="G15" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="H15" t="n">
         <v>500</v>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>44.52380952380953</v>
+        <v>37.40000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1092,17 +1092,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ISRAEL 1</t>
+          <t>SWITZERLAND 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Hapoel Haifa x Maccabi Tel Aviv</t>
+          <t>Grasshoppers Zurich x Sion</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="G16" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="H16" t="n">
         <v>500</v>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>49.21052631578947</v>
+        <v>44.52380952380953</v>
       </c>
     </row>
     <row r="17">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BRAZIL 1</t>
+          <t>DENMARK 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Chapecoense x EC Vitoria Salvador</t>
+          <t>Vejle x Randers</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BRAZIL 1</t>
+          <t>ITALY 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Bahia x SE Palmeiras</t>
+          <t>Reggiana x Pescara</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="G18" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="H18" t="n">
         <v>500</v>
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>44.52380952380953</v>
+        <v>49.21052631578947</v>
       </c>
     </row>
     <row r="19">
@@ -1224,17 +1224,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BRAZIL 1</t>
+          <t>DENMARK 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Corinthians x Internacional</t>
+          <t>Viborg x AGF</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1243,42 +1243,42 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="G19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="H19" t="n">
         <v>500</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>-500</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1 ⭐</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SCOTLAND 1</t>
+          <t>GERMANY 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Livingston x Hearts</t>
+          <t>Duisburg x VfL Osnabruck</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H20" t="n">
         <v>500</v>
@@ -1301,28 +1301,28 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>59.93589743589743</v>
+        <v>57.01219512195123</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1 ⭐</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ITALY 1</t>
+          <t>GERMANY 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Pisa x Torino</t>
+          <t>Schweinfurt x Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1331,21 +1331,21 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>8.6</v>
+        <v>12.5</v>
       </c>
       <c r="G21" t="n">
-        <v>8.6</v>
+        <v>12.5</v>
       </c>
       <c r="H21" t="n">
         <v>500</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>-500</v>
+        <v>40.65217391304348</v>
       </c>
     </row>
     <row r="22">
@@ -1356,17 +1356,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CHILE 1</t>
+          <t>EUROPA CHAMPIONS LEAGUE</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Deportes Concepcion x Colo Colo</t>
+          <t>Sporting Lisbon x Arsenal</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="G22" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="H22" t="n">
         <v>500</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>59.93589743589743</v>
+        <v>-500</v>
       </c>
     </row>
     <row r="23">
@@ -1400,17 +1400,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>POLAND 1</t>
+          <t>SLOVENIA 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Nieciecza x Piast Gliwice</t>
+          <t>NK Primorje x Koper</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="G23" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="H23" t="n">
         <v>500</v>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>49.21052631578947</v>
+        <v>37.40000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1444,17 +1444,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SWITZERLAND 1</t>
+          <t>FRANCE 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Grasshoppers Zurich x Sion</t>
+          <t>Sochaux x Fleury Merogis</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>11.5</v>
+        <v>19.5</v>
       </c>
       <c r="G24" t="n">
-        <v>11.5</v>
+        <v>19.5</v>
       </c>
       <c r="H24" t="n">
         <v>500</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>44.52380952380953</v>
+        <v>25.27027027027027</v>
       </c>
     </row>
     <row r="25">
@@ -1488,17 +1488,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DENMARK 1</t>
+          <t>FRANCE 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Vejle x Randers</t>
+          <t>Stade Briochin x Villefranche Beaujolais</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1507,10 +1507,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="G25" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="H25" t="n">
         <v>500</v>
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>46.75</v>
+        <v>40.65217391304348</v>
       </c>
     </row>
     <row r="26">
@@ -1532,17 +1532,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ITALY 2</t>
+          <t>FRANCE 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Catanzaro x AC Monza</t>
+          <t>Valenciennes x Versailles 78 FC</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="G26" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="H26" t="n">
         <v>500</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>46.75</v>
+        <v>37.40000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -1576,17 +1576,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ITALY 2</t>
+          <t>GERMANY 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Reggiana x Pescara</t>
+          <t>FC Heidenheim x Union Berlin</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="G27" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="H27" t="n">
         <v>500</v>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>49.21052631578947</v>
+        <v>44.52380952380953</v>
       </c>
     </row>
     <row r="28">
@@ -1620,17 +1620,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NORWAY 1</t>
+          <t>SLOVAKIA 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Ham-Kam x Brann</t>
+          <t>Ruzomberok x MFK Skalica</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="G28" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="H28" t="n">
         <v>500</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>49.21052631578947</v>
+        <v>35.96153846153846</v>
       </c>
     </row>
     <row r="29">
@@ -1664,17 +1664,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ITALY 2</t>
+          <t>SLOVAKIA 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sampdoria x Empoli</t>
+          <t>Trencin x Tatran Presov</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1683,21 +1683,21 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G29" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H29" t="n">
         <v>500</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>46.75</v>
+        <v>-500</v>
       </c>
     </row>
     <row r="30">
@@ -1708,17 +1708,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TURKEY 1</t>
+          <t>GERMANY 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Kocaelispor x Basaksehir</t>
+          <t>St Pauli x Bayern Munich</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="G30" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="H30" t="n">
         <v>500</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>53.125</v>
+        <v>49.21052631578947</v>
       </c>
     </row>
     <row r="31">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PARAGUAY 1</t>
+          <t>NETHERLANDS 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense x Rubio Nu</t>
+          <t>FC Dordrecht x ADO Den Haag</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1771,10 +1771,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="G31" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="H31" t="n">
         <v>500</v>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>46.75</v>
+        <v>44.52380952380953</v>
       </c>
     </row>
     <row r="32">
@@ -1796,17 +1796,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BRAZIL 2</t>
+          <t>ENGLAND 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Goias x Criciuma</t>
+          <t>Crystal Palace x Newcastle</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1835,22 +1835,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1 ⭐</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PORTUGAL 2</t>
+          <t>ENGLAND 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Porto B x Chaves</t>
+          <t>Nottm Forest x Aston Villa</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="G33" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="H33" t="n">
         <v>500</v>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>59.93589743589743</v>
+        <v>46.75</v>
       </c>
     </row>
     <row r="34">
@@ -1884,17 +1884,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>POLAND 1</t>
+          <t>ITALY 2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Arka Gdynia x Zaglebie Lubin</t>
+          <t>Padova x Empoli</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="G34" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="H34" t="n">
         <v>500</v>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>53.125</v>
+        <v>54.36046511627907</v>
       </c>
     </row>
     <row r="35">
@@ -1928,17 +1928,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GERMANY 3</t>
+          <t>ENGLAND 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Duisburg x VfL Osnabruck</t>
+          <t>Sunderland x Tottenham</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="G35" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="H35" t="n">
         <v>500</v>
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>57.01219512195123</v>
+        <v>44.52380952380953</v>
       </c>
     </row>
     <row r="36">
@@ -1972,17 +1972,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SCOTLAND 2</t>
+          <t>SLOVAKIA 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ayr x Dunfermline</t>
+          <t>KFC Komarno x FC Kosice</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="G36" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="H36" t="n">
         <v>500</v>
@@ -2005,28 +2005,28 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>51.94444444444444</v>
+        <v>40.65217391304348</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1 ⭐</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TURKEY 1</t>
+          <t>DENMARK 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Goztepe x Galatasaray</t>
+          <t>Brondby x Midtjylland</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2035,10 +2035,10 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="G37" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="H37" t="n">
         <v>500</v>
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>59.93589743589743</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="38">
@@ -2060,17 +2060,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FINLAND 1</t>
+          <t>GERMANY 3</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>TPS x Lahti</t>
+          <t>Erzgebirge x Verl</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G38" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H38" t="n">
         <v>500</v>
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>46.75</v>
+        <v>38.95833333333334</v>
       </c>
     </row>
     <row r="39">
@@ -2104,17 +2104,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FRANCE 2</t>
+          <t>AUSTRIA 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Annecy x Montpellier</t>
+          <t>Austria Wien x Rapid Vienna</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="G39" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="H39" t="n">
         <v>500</v>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>49.21052631578947</v>
+        <v>51.94444444444444</v>
       </c>
     </row>
     <row r="40">
@@ -2148,17 +2148,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FRANCE 2</t>
+          <t>DENMARK 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Clermont x Nancy</t>
+          <t>Randers x FC Copenhagen</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="G40" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="H40" t="n">
         <v>500</v>
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>46.75</v>
+        <v>49.21052631578947</v>
       </c>
     </row>
     <row r="41">
@@ -2192,17 +2192,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SCOTLAND 2</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Queens Park x Ross Co</t>
+          <t>Cadiz x Andorra CF</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2221,11 +2221,11 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>54.36046511627907</v>
+        <v>-500</v>
       </c>
     </row>
     <row r="42">
@@ -2236,17 +2236,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CHINA 1</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island x Liaoning Tieren FC</t>
+          <t>Mirandes x CD Castellon</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2280,17 +2280,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GERMANY 1</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>FC Heidenheim x Union Berlin</t>
+          <t>Valladolid x Eibar</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="G43" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="H43" t="n">
         <v>500</v>
@@ -2313,40 +2313,40 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>44.52380952380953</v>
+        <v>54.36046511627907</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>P1 ⭐</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SCOTLAND 2</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ayr x Arbroath</t>
+          <t>Valladolid x Eibar</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lay_CS_0x1_B365</t>
+          <t>Lay_CS_1x0_B365</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="G44" t="n">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="H44" t="n">
         <v>500</v>
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>46.75</v>
+        <v>70.83333333333334</v>
       </c>
     </row>
     <row r="45">
@@ -2368,17 +2368,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GERMANY 1</t>
+          <t>SLOVENIA 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>St Pauli x Bayern Munich</t>
+          <t>NK Aluminij x Mura</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2387,10 +2387,10 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="G45" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="H45" t="n">
         <v>500</v>
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>49.21052631578947</v>
+        <v>34.62962962962963</v>
       </c>
     </row>
     <row r="46">
@@ -2412,17 +2412,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BRAZIL 1</t>
+          <t>ITALY 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Remo x Vasco Da Gama</t>
+          <t>Sassuolo x Como</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="G46" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="H46" t="n">
         <v>500</v>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>46.75</v>
+        <v>54.36046511627907</v>
       </c>
     </row>
     <row r="47">
@@ -2456,17 +2456,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PORTUGAL 2</t>
+          <t>NETHERLANDS 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Feirense x Vizela</t>
+          <t>Helmond Sport x VVV Venlo</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2475,10 +2475,10 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>9.6</v>
+        <v>15</v>
       </c>
       <c r="G47" t="n">
-        <v>9.6</v>
+        <v>15</v>
       </c>
       <c r="H47" t="n">
         <v>500</v>
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>54.36046511627907</v>
+        <v>33.39285714285715</v>
       </c>
     </row>
     <row r="48">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>FC Dordrecht x ADO Den Haag</t>
+          <t>Jong PSV Eindhoven x Jong Ajax Amsterdam</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2519,21 +2519,21 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>11.5</v>
+        <v>85</v>
       </c>
       <c r="G48" t="n">
-        <v>11.5</v>
+        <v>85</v>
       </c>
       <c r="H48" t="n">
         <v>500</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>44.52380952380953</v>
+        <v>-500</v>
       </c>
     </row>
     <row r="49">
@@ -2544,17 +2544,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SCOTLAND 1</t>
+          <t>NETHERLANDS 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Falkirk x Rangers</t>
+          <t>Vitesse Arnhem x MVV Maastricht</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="G49" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="H49" t="n">
         <v>500</v>
@@ -2577,7 +2577,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>46.75</v>
+        <v>10.87209302325581</v>
       </c>
     </row>
     <row r="50">
@@ -2588,17 +2588,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CHINA 1</t>
+          <t>GERMANY 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Shijiazhuang Gongfu FC x Foshan Nanshi FC</t>
+          <t>St Pauli x FC Koln</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2617,11 +2617,11 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>-500</v>
+        <v>49.21052631578947</v>
       </c>
     </row>
     <row r="51">
@@ -2632,17 +2632,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ENGLAND 1</t>
+          <t>SLOVAKIA 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Crystal Palace x Newcastle</t>
+          <t>Podbrezova x Dunajska Streda</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2651,10 +2651,10 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="G51" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="H51" t="n">
         <v>500</v>
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>44.52380952380953</v>
+        <v>40.65217391304348</v>
       </c>
     </row>
     <row r="52">
@@ -2676,17 +2676,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SWEDEN 2</t>
+          <t>SLOVAKIA 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>IK Brage x Oddevold</t>
+          <t>Ruzomberok x KFC Komarno</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G52" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H52" t="n">
         <v>500</v>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>46.75</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="53">
@@ -2720,17 +2720,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ENGLAND 1</t>
+          <t>SCOTLAND 2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Nottm Forest x Aston Villa</t>
+          <t>Ross Co x Ayr</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="G53" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="H53" t="n">
         <v>500</v>
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>46.75</v>
+        <v>40.65217391304348</v>
       </c>
     </row>
     <row r="54">
@@ -2764,17 +2764,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ITALY 2</t>
+          <t>SERBIA 1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Padova x Empoli</t>
+          <t>FK Novi Pazar x OFK Beograd</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2783,10 +2783,10 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="G54" t="n">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="H54" t="n">
         <v>500</v>
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>54.36046511627907</v>
+        <v>37.40000000000001</v>
       </c>
     </row>
     <row r="55">
@@ -2808,17 +2808,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ENGLAND 1</t>
+          <t>ITALY 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sunderland x Tottenham</t>
+          <t>US Cremonese x Torino</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="G55" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="H55" t="n">
         <v>500</v>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>44.52380952380953</v>
+        <v>58.4375</v>
       </c>
     </row>
     <row r="56">
@@ -2852,17 +2852,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AUSTRIA 1</t>
+          <t>ESTONIA 1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Austria Wien x Rapid Vienna</t>
+          <t>Paide Linnameeskond x Nomme Kalju</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G56" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H56" t="n">
         <v>500</v>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>51.94444444444444</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="57">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Randers x FC Copenhagen</t>
+          <t>Vejle x FC Copenhagen</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="G57" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="H57" t="n">
         <v>500</v>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>49.21052631578947</v>
+        <v>44.52380952380953</v>
       </c>
     </row>
     <row r="58">
@@ -2940,17 +2940,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ROMANIA 1</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>FC Metaloglobus Bucuresti x Csikszereda</t>
+          <t>Albacete x Granada</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2959,42 +2959,42 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="G58" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="H58" t="n">
         <v>500</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>-500</v>
+        <v>46.75</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>P1 ⭐</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>ITALY 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>CSKA Sofia x PFC Levski Sofia</t>
+          <t>Pisa x Genoa</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3003,10 +3003,10 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G59" t="n">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H59" t="n">
         <v>500</v>
@@ -3017,40 +3017,40 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>44.52380952380953</v>
+        <v>64.93055555555556</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>P1 ⭐</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>PORTUGAL 2</t>
+          <t>ITALY 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Lusitania Futebol Clube x Porto B</t>
+          <t>US Cremonese x Torino</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lay_CS_0x1_B365</t>
+          <t>Lay_CS_1x0_B365</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="G60" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="H60" t="n">
         <v>500</v>
@@ -3061,33 +3061,33 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>46.75</v>
+        <v>49.21052631578947</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>P1 ⭐</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ROMANIA 1</t>
+          <t>ITALY 1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Universitatea Cluj x Universitatea Craiova</t>
+          <t>Pisa x Genoa</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Lay_CS_0x1_B365</t>
+          <t>Lay_CS_1x0_B365</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -3111,34 +3111,34 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>TURKEY 1</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Eyupspor x Samsunspor</t>
+          <t>Albacete x Granada</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Lay_CS_0x1_B365</t>
+          <t>Lay_CS_1x0_B365</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G62" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H62" t="n">
         <v>500</v>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>59.93589743589743</v>
+        <v>57.01219512195123</v>
       </c>
     </row>
     <row r="63">
@@ -3160,17 +3160,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>ENGLAND 1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Botev Vratsa x Lokomotiv Sofia</t>
+          <t>Crystal Palace x West Ham</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="G63" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="H63" t="n">
         <v>500</v>
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>57.01219512195123</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="64">
@@ -3204,17 +3204,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>AUSTRIA 1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Dobrudzha x Botev Plovdiv</t>
+          <t>SCR Altach x WSG Wattens</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="G64" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="H64" t="n">
         <v>500</v>
@@ -3237,7 +3237,7 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>53.125</v>
+        <v>44.52380952380953</v>
       </c>
     </row>
     <row r="65">
@@ -3248,17 +3248,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>AUSTRIA 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Cherno More x CSKA 1948 Sofia</t>
+          <t>SV Ried x Grazer AK</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3267,10 +3267,10 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G65" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H65" t="n">
         <v>500</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>46.75</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="66">
@@ -3292,17 +3292,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CHINA 1</t>
+          <t>ICELAND 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns x Chengdu Rongcheng</t>
+          <t>Keflavik x Breidablik</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3311,21 +3311,21 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="G66" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="H66" t="n">
         <v>500</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>-500</v>
+        <v>34.62962962962963</v>
       </c>
     </row>
     <row r="67">
@@ -3336,17 +3336,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ITALY 1</t>
+          <t>AUSTRIA 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Sassuolo x Como</t>
+          <t>Sturm Graz x LASK Linz</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="G67" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="H67" t="n">
         <v>500</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>54.36046511627907</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="68">
@@ -3380,17 +3380,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GERMANY 1</t>
+          <t>FRANCE 3</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>St Pauli x FC Koln</t>
+          <t>Chateauroux x Fleury Merogis</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3399,10 +3399,10 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="G68" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="H68" t="n">
         <v>500</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>49.21052631578947</v>
+        <v>34.62962962962963</v>
       </c>
     </row>
     <row r="69">
@@ -3424,17 +3424,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FINLAND 1</t>
+          <t>FRANCE 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Jaro x KuPS</t>
+          <t>Le Puy x Versailles 78 FC</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="G69" t="n">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="H69" t="n">
         <v>500</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>55.65476190476191</v>
+        <v>38.95833333333334</v>
       </c>
     </row>
     <row r="70">
@@ -3468,17 +3468,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SCOTLAND 2</t>
+          <t>NETHERLANDS 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Airdrieonians x Partick</t>
+          <t>Den Bosch x ADO Den Haag</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="G70" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="H70" t="n">
         <v>500</v>
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>51.94444444444444</v>
+        <v>40.65217391304348</v>
       </c>
     </row>
     <row r="71">
@@ -3512,17 +3512,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FINLAND 1</t>
+          <t>NETHERLANDS 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>TPS x SJK</t>
+          <t>RKC Waalwijk x Jong PSV Eindhoven</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>11.5</v>
+        <v>38</v>
       </c>
       <c r="G71" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="H71" t="n">
         <v>500</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>44.52380952380953</v>
+        <v>24.60526315789474</v>
       </c>
     </row>
     <row r="72">
@@ -3556,17 +3556,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FINLAND 1</t>
+          <t>GERMANY 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>IFK Mariehamn x Ilves</t>
+          <t>Preussen Munster x Arminia Bielefeld</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3575,10 +3575,10 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="G72" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="H72" t="n">
         <v>500</v>
@@ -3589,7 +3589,7 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>49.21052631578947</v>
+        <v>40.65217391304348</v>
       </c>
     </row>
     <row r="73">
@@ -3600,17 +3600,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>WALES 1</t>
+          <t>SCOTLAND 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Barry Town Utd x The New Saints</t>
+          <t>Airdrieonians x Ayr</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3619,21 +3619,21 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="G73" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="H73" t="n">
         <v>500</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>-500</v>
+        <v>40.65217391304348</v>
       </c>
     </row>
     <row r="74">
@@ -3644,17 +3644,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>TURKEY 1</t>
+          <t>ITALY 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Genclerbirligi x Galatasaray</t>
+          <t>Bologna x Roma</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3663,10 +3663,10 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="G74" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="H74" t="n">
         <v>500</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>57.01219512195123</v>
+        <v>58.4375</v>
       </c>
     </row>
     <row r="75">
@@ -3688,17 +3688,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>PORTUGAL 2</t>
+          <t>SWITZERLAND 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Torreense x Maritimo</t>
+          <t>Grasshoppers Zurich x Luzern</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3707,10 +3707,10 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>10.5</v>
+        <v>26</v>
       </c>
       <c r="G75" t="n">
-        <v>10.5</v>
+        <v>26</v>
       </c>
       <c r="H75" t="n">
         <v>500</v>
@@ -3721,28 +3721,28 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>49.21052631578947</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1 ⭐</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>FRANCE 2</t>
+          <t>SLOVAKIA 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Bastia x St Etienne</t>
+          <t>KFC Komarno x MFk Skalica</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3751,10 +3751,10 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>8.6</v>
+        <v>17.5</v>
       </c>
       <c r="G76" t="n">
-        <v>8.6</v>
+        <v>17.5</v>
       </c>
       <c r="H76" t="n">
         <v>500</v>
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>61.51315789473684</v>
+        <v>28.33333333333334</v>
       </c>
     </row>
     <row r="77">
@@ -3776,17 +3776,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ITALY 1</t>
+          <t>SLOVAKIA 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>US Cremonese x Torino</t>
+          <t>Zemplin x Podbrezova</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G77" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H77" t="n">
         <v>500</v>
@@ -3809,7 +3809,7 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>58.4375</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="78">
@@ -3820,17 +3820,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>TURKEY 1</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Kasimpasa x Alanyaspor</t>
+          <t>Burgos x Deportivo</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3839,10 +3839,10 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G78" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H78" t="n">
         <v>500</v>
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>46.75</v>
+        <v>58.4375</v>
       </c>
     </row>
     <row r="79">
@@ -3864,17 +3864,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NORWAY 1</t>
+          <t>SWITZERLAND 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Ham-Kam x KFUM Oslo</t>
+          <t>Thun x Lugano</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3883,42 +3883,42 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="G79" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="H79" t="n">
         <v>500</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>44.52380952380953</v>
+        <v>-500</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>P1 ⭐</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NORWAY 1</t>
+          <t>ITALY 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Sarpsborg x Tromso</t>
+          <t>Verona x Lecce</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3927,54 +3927,54 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="G80" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="H80" t="n">
         <v>500</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>-500</v>
+        <v>61.51315789473684</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>P1 ⭐</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ROMANIA 1</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ACS Petrolul 52 x Hermannstadt</t>
+          <t>Burgos x Deportivo</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Lay_CS_0x1_B365</t>
+          <t>Lay_CS_1x0_B365</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G81" t="n">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H81" t="n">
         <v>500</v>
@@ -3985,40 +3985,40 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>44.52380952380953</v>
+        <v>64.93055555555556</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>P1 ⭐</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>POLAND 1</t>
+          <t>ITALY 1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Arka Gdynia x Jagiellonia Bialystock</t>
+          <t>Verona x Lecce</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Lay_CS_0x1_B365</t>
+          <t>Lay_CS_1x0_B365</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="G82" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="H82" t="n">
         <v>500</v>
@@ -4029,7 +4029,7 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>49.21052631578947</v>
+        <v>73.046875</v>
       </c>
     </row>
     <row r="83">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Vejle x FC Copenhagen</t>
+          <t>Silkeborg x Randers</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="G83" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="H83" t="n">
         <v>500</v>
@@ -4073,28 +4073,28 @@
         </is>
       </c>
       <c r="J83" t="n">
-        <v>44.52380952380953</v>
+        <v>46.75</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1 ⭐</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ITALY 1</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Pisa x Genoa</t>
+          <t>Granada x Almeria</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4103,10 +4103,10 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="G84" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="H84" t="n">
         <v>500</v>
@@ -4117,40 +4117,40 @@
         </is>
       </c>
       <c r="J84" t="n">
-        <v>64.93055555555556</v>
+        <v>46.75</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P1 ⭐</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ITALY 1</t>
+          <t>SERBIA 1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>US Cremonese x Torino</t>
+          <t>FK Novi Pazar x Cukaricki</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Lay_CS_1x0_B365</t>
+          <t>Lay_CS_0x1_B365</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="G85" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="H85" t="n">
         <v>500</v>
@@ -4161,40 +4161,40 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>49.21052631578947</v>
+        <v>35.96153846153846</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P1 ⭐</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ITALY 1</t>
+          <t>AUSTRIA 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Pisa x Genoa</t>
+          <t>Sturm Graz x Austria Wien</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Lay_CS_1x0_B365</t>
+          <t>Lay_CS_0x1_B365</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="G86" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="H86" t="n">
         <v>500</v>
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>58.4375</v>
+        <v>37.40000000000001</v>
       </c>
     </row>
     <row r="87">
@@ -4216,17 +4216,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ROMANIA 1</t>
+          <t>SLOVENIA 1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Farul Constanta x FCSB</t>
+          <t>NK Celje x NK Aluminij</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4235,10 +4235,10 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="G87" t="n">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="H87" t="n">
         <v>500</v>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>51.94444444444444</v>
+        <v>7.3046875</v>
       </c>
     </row>
     <row r="88">
@@ -4260,17 +4260,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PORTUGAL 2</t>
+          <t>ITALY 1</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Porto B x Leixoes</t>
+          <t>Torino x Inter</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G88" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H88" t="n">
         <v>500</v>
@@ -4293,28 +4293,28 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>46.75</v>
+        <v>53.125</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>P1 ⭐</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>PORTUGAL 2</t>
+          <t>ITALY 1</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Sporting Lisbon B x Felgueiras</t>
+          <t>Genoa x Como</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4323,21 +4323,21 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G89" t="n">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H89" t="n">
         <v>500</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="J89" t="n">
-        <v>-500</v>
+        <v>64.93055555555556</v>
       </c>
     </row>
     <row r="90">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CHINA 1</t>
+          <t>SERBIA 1</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Tianjin Jinmen Tiger FC x Shandong Taishan</t>
+          <t>FK Radnicki 1923 x FK Spartak</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4367,10 +4367,10 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>11.5</v>
+        <v>50</v>
       </c>
       <c r="G90" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="H90" t="n">
         <v>500</v>
@@ -4381,7 +4381,7 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>44.52380952380953</v>
+        <v>24.60526315789474</v>
       </c>
     </row>
     <row r="91">
@@ -4392,17 +4392,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AUSTRIA 1</t>
+          <t>ITALY 1</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SCR Altach x WSG Wattens</t>
+          <t>Cagliari x Atalanta</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="G91" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="H91" t="n">
         <v>500</v>
@@ -4425,28 +4425,28 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>44.52380952380953</v>
+        <v>58.4375</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>P1 ⭐</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SWEDEN 2</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Orebro x Norrkoping</t>
+          <t>Cadiz x Las Palmas</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4455,10 +4455,10 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="G92" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="H92" t="n">
         <v>500</v>
@@ -4469,1503 +4469,7 @@
         </is>
       </c>
       <c r="J92" t="n">
-        <v>44.52380952380953</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>P1 ⭐</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>CHINA 1</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Qingdao Youth Island x Henan Songshan Longmen</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Lay_CS_0x1_B365</t>
-        </is>
-      </c>
-      <c r="F93" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="G93" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H93" t="n">
-        <v>500</v>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="J93" t="n">
-        <v>44.52380952380953</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>P1 ⭐</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>SERBIA 1</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Radnik Surdulica x FK Novi Pazar</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Lay_CS_0x1_B365</t>
-        </is>
-      </c>
-      <c r="F94" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="G94" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H94" t="n">
-        <v>500</v>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="J94" t="n">
-        <v>44.52380952380953</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>P1 ⭐</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>SERBIA 1</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Zeleznicar Pancevo x Crvena Zvezda</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Lay_CS_0x1_B365</t>
-        </is>
-      </c>
-      <c r="F95" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="G95" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H95" t="n">
-        <v>500</v>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="J95" t="n">
-        <v>44.52380952380953</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>P1 ⭐</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>SERBIA 1</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>FK Napredak x FK IMT Novi Beograd</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Lay_CS_0x1_B365</t>
-        </is>
-      </c>
-      <c r="F96" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="G96" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="H96" t="n">
-        <v>500</v>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>RED</t>
-        </is>
-      </c>
-      <c r="J96" t="n">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>P1 ⭐</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>SERBIA 1</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>FK Spartak x FK Backa Topola</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Lay_CS_0x1_B365</t>
-        </is>
-      </c>
-      <c r="F97" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="G97" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="H97" t="n">
-        <v>500</v>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="J97" t="n">
-        <v>53.125</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>P1 ⭐</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>FINLAND 1</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>VPS x Ilves</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Lay_CS_0x1_B365</t>
-        </is>
-      </c>
-      <c r="F98" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G98" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="H98" t="n">
-        <v>500</v>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="J98" t="n">
-        <v>49.21052631578947</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>P1 ⭐</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>FRANCE 2</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Amiens x Montpellier</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Lay_CS_0x1_B365</t>
-        </is>
-      </c>
-      <c r="F99" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G99" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="H99" t="n">
-        <v>500</v>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="J99" t="n">
-        <v>49.21052631578947</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>P1 ⭐</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>FRANCE 2</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Clermont x Bastia</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Lay_CS_0x1_B365</t>
-        </is>
-      </c>
-      <c r="F100" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="G100" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H100" t="n">
-        <v>500</v>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="J100" t="n">
-        <v>54.36046511627907</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>P1 ⭐</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>FRANCE 2</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Grenoble x Le Mans</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Lay_CS_0x1_B365</t>
-        </is>
-      </c>
-      <c r="F101" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G101" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="H101" t="n">
-        <v>500</v>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="J101" t="n">
-        <v>49.21052631578947</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>P1 ⭐</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>FINLAND 1</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Lahti x AC Oulu</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Lay_CS_0x1_B365</t>
-        </is>
-      </c>
-      <c r="F102" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G102" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="H102" t="n">
-        <v>500</v>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="J102" t="n">
-        <v>49.21052631578947</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>P1 ⭐</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>BULGARIA 1</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>CSKA Sofia x PFC Levski Sofia</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Lay_CS_0x1_B365</t>
-        </is>
-      </c>
-      <c r="F103" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="G103" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H103" t="n">
-        <v>500</v>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="J103" t="n">
-        <v>44.52380952380953</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>P1 ⭐</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>SCOTLAND 2</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Arbroath x Partick</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Lay_CS_0x1_B365</t>
-        </is>
-      </c>
-      <c r="F104" t="n">
-        <v>11</v>
-      </c>
-      <c r="G104" t="n">
-        <v>11</v>
-      </c>
-      <c r="H104" t="n">
-        <v>500</v>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="J104" t="n">
-        <v>46.75</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>P1 ⭐</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>NORWAY 1</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Fredrikstad x Viking</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Lay_CS_0x1_B365</t>
-        </is>
-      </c>
-      <c r="F105" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="G105" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H105" t="n">
-        <v>500</v>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="J105" t="n">
-        <v>44.52380952380953</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>P1 ⭐</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>ITALY 1</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Bologna x Roma</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Lay_CS_0x1_B365</t>
-        </is>
-      </c>
-      <c r="F106" t="n">
-        <v>9</v>
-      </c>
-      <c r="G106" t="n">
-        <v>9</v>
-      </c>
-      <c r="H106" t="n">
-        <v>500</v>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="J106" t="n">
-        <v>58.4375</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>P1 ⭐</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>PORTUGAL 2</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Felgueiras x Leiria</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Lay_CS_0x1_B365</t>
-        </is>
-      </c>
-      <c r="F107" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G107" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="H107" t="n">
-        <v>500</v>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="J107" t="n">
-        <v>49.21052631578947</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>SCOTLAND 2</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Queens Park x Dunfermline</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Lay_CS_0x1_B365</t>
-        </is>
-      </c>
-      <c r="F108" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="G108" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H108" t="n">
-        <v>500</v>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="J108" t="n">
         <v>63.17567567567568</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>ITALY 1</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Verona x Lecce</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Lay_CS_0x1_B365</t>
-        </is>
-      </c>
-      <c r="F109" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="G109" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H109" t="n">
-        <v>500</v>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="J109" t="n">
-        <v>61.51315789473684</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>ITALY 1</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Verona x Lecce</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Lay_CS_1x0_B365</t>
-        </is>
-      </c>
-      <c r="F110" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="G110" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H110" t="n">
-        <v>500</v>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="J110" t="n">
-        <v>73.046875</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>P1 ⭐</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>CHINA 1</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Changchun Yatai x Guangdong GZ-Power FC</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Lay_CS_0x1_B365</t>
-        </is>
-      </c>
-      <c r="F111" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="G111" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H111" t="n">
-        <v>500</v>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="J111" t="n">
-        <v>57.01219512195123</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>P1 ⭐</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>CHINA 1</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Qingdao Hainiu x Shandong Taishan</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Lay_CS_0x1_B365</t>
-        </is>
-      </c>
-      <c r="F112" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="G112" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="H112" t="n">
-        <v>500</v>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="J112" t="n">
-        <v>55.65476190476191</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>P1 ⭐</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>PORTUGAL 2</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Lusitania Futebol Clube x Pacos Ferreira</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Lay_CS_0x1_B365</t>
-        </is>
-      </c>
-      <c r="F113" t="n">
-        <v>11</v>
-      </c>
-      <c r="G113" t="n">
-        <v>11</v>
-      </c>
-      <c r="H113" t="n">
-        <v>500</v>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="J113" t="n">
-        <v>46.75</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>P1 ⭐</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>POLAND 1</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Wisla Plock x Radomiak Radom</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Lay_CS_0x1_B365</t>
-        </is>
-      </c>
-      <c r="F114" t="n">
-        <v>11</v>
-      </c>
-      <c r="G114" t="n">
-        <v>11</v>
-      </c>
-      <c r="H114" t="n">
-        <v>500</v>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>RED</t>
-        </is>
-      </c>
-      <c r="J114" t="n">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>P1 ⭐</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>TURKEY 1</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Genclerbirligi x Kocaelispor</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Lay_CS_0x1_B365</t>
-        </is>
-      </c>
-      <c r="F115" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="G115" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="H115" t="n">
-        <v>500</v>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="J115" t="n">
-        <v>53.125</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>P1 ⭐</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>CHINA 1</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Henan Songshan Longmen x Shanghai Shenhua</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Lay_CS_0x1_B365</t>
-        </is>
-      </c>
-      <c r="F116" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="G116" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H116" t="n">
-        <v>500</v>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="J116" t="n">
-        <v>44.52380952380953</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>P1 ⭐</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>DENMARK 1</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Silkeborg x Randers</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Lay_CS_0x1_B365</t>
-        </is>
-      </c>
-      <c r="F117" t="n">
-        <v>11</v>
-      </c>
-      <c r="G117" t="n">
-        <v>11</v>
-      </c>
-      <c r="H117" t="n">
-        <v>500</v>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="J117" t="n">
-        <v>46.75</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>P1 ⭐</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>BULGARIA 1</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Lokomotiv Plovdiv x Cherno More</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Lay_CS_0x1_B365</t>
-        </is>
-      </c>
-      <c r="F118" t="n">
-        <v>11</v>
-      </c>
-      <c r="G118" t="n">
-        <v>11</v>
-      </c>
-      <c r="H118" t="n">
-        <v>500</v>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>RED</t>
-        </is>
-      </c>
-      <c r="J118" t="n">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>P1 ⭐</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>SWEDEN 1</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>IFK Goteborg x GAIS</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Lay_CS_0x1_B365</t>
-        </is>
-      </c>
-      <c r="F119" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="G119" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H119" t="n">
-        <v>500</v>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="J119" t="n">
-        <v>44.52380952380953</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>P1 ⭐</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>SCOTLAND 1</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Hibernian x Hearts</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Lay_CS_0x1_B365</t>
-        </is>
-      </c>
-      <c r="F120" t="n">
-        <v>11</v>
-      </c>
-      <c r="G120" t="n">
-        <v>11</v>
-      </c>
-      <c r="H120" t="n">
-        <v>500</v>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="J120" t="n">
-        <v>46.75</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>P1 ⭐</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>BULGARIA 1</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Arda x Botev Plovdiv</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Lay_CS_0x1_B365</t>
-        </is>
-      </c>
-      <c r="F121" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="G121" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="H121" t="n">
-        <v>500</v>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="J121" t="n">
-        <v>55.65476190476191</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>P1 ⭐</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>ITALY 1</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>Torino x Inter</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Lay_CS_0x1_B365</t>
-        </is>
-      </c>
-      <c r="F122" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="G122" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="H122" t="n">
-        <v>500</v>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="J122" t="n">
-        <v>53.125</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>ITALY 1</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Genoa x Como</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Lay_CS_0x1_B365</t>
-        </is>
-      </c>
-      <c r="F123" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="G123" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="H123" t="n">
-        <v>500</v>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="J123" t="n">
-        <v>64.93055555555556</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>P1 ⭐</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>ROMANIA 1</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>FC Metaloglobus Bucuresti x Unirea Slobozia</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Lay_CS_0x1_B365</t>
-        </is>
-      </c>
-      <c r="F124" t="n">
-        <v>10</v>
-      </c>
-      <c r="G124" t="n">
-        <v>10</v>
-      </c>
-      <c r="H124" t="n">
-        <v>500</v>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="J124" t="n">
-        <v>51.94444444444444</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>P1 ⭐</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>ITALY 1</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>Cagliari x Atalanta</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Lay_CS_0x1_B365</t>
-        </is>
-      </c>
-      <c r="F125" t="n">
-        <v>9</v>
-      </c>
-      <c r="G125" t="n">
-        <v>9</v>
-      </c>
-      <c r="H125" t="n">
-        <v>500</v>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="J125" t="n">
-        <v>58.4375</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>P1 ⭐</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>FRANCE 2</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Boulogne x Dunkerque</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Lay_CS_0x1_B365</t>
-        </is>
-      </c>
-      <c r="F126" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G126" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="H126" t="n">
-        <v>500</v>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="J126" t="n">
-        <v>49.21052631578947</v>
       </c>
     </row>
   </sheetData>
